--- a/artfynd/A 17248-2026 artfynd.xlsx
+++ b/artfynd/A 17248-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY31"/>
+  <dimension ref="A1:AY37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,41 +675,37 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>133315942</v>
+        <v>133315970</v>
       </c>
       <c r="B2" t="n">
-        <v>80485</v>
+        <v>79373</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -717,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>495453</v>
+        <v>495669</v>
       </c>
       <c r="R2" t="n">
-        <v>7037883</v>
+        <v>7037792</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -757,7 +753,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>På rönn.</t>
+          <t>På gran i granskog.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,17 +773,17 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>rönn</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>Sorbus aucuparia</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Sorbus aucuparia</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -805,14 +801,14 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133315984</v>
+        <v>133315972</v>
       </c>
       <c r="B3" t="n">
-        <v>79358</v>
+        <v>79373</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -843,10 +839,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>495402</v>
+        <v>495661</v>
       </c>
       <c r="R3" t="n">
-        <v>7037913</v>
+        <v>7037824</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -881,6 +877,11 @@
           <t>2026-04-23</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>På flera granar.</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -893,7 +894,7 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
@@ -906,9 +907,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -926,10 +932,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>133315960</v>
+        <v>133315973</v>
       </c>
       <c r="B4" t="n">
-        <v>99178</v>
+        <v>79373</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -937,54 +943,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr"/>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Erik-Nilsabodarna, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>495588</v>
+        <v>495614</v>
       </c>
       <c r="R4" t="n">
-        <v>7037838</v>
+        <v>7037811</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1019,11 +1008,6 @@
           <t>2026-04-23</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Minst 36 plantor inom ca 1 m2 yta intill en stående död gran och en tall.</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1037,6 +1021,21 @@
       <c r="AH4" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1054,14 +1053,14 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>133315977</v>
+        <v>133315974</v>
       </c>
       <c r="B5" t="n">
-        <v>79358</v>
+        <v>79373</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1092,10 +1091,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>495459</v>
+        <v>495582</v>
       </c>
       <c r="R5" t="n">
-        <v>7037865</v>
+        <v>7037849</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1130,6 +1129,11 @@
           <t>2026-04-23</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>På flera granar.</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1155,9 +1159,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1175,14 +1184,14 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133315982</v>
+        <v>133315976</v>
       </c>
       <c r="B6" t="n">
-        <v>79358</v>
+        <v>79373</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1213,10 +1222,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>495349</v>
+        <v>495495</v>
       </c>
       <c r="R6" t="n">
-        <v>7037870</v>
+        <v>7037847</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1301,14 +1310,14 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133315974</v>
+        <v>133315977</v>
       </c>
       <c r="B7" t="n">
-        <v>79358</v>
+        <v>79373</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1339,10 +1348,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>495582</v>
+        <v>495459</v>
       </c>
       <c r="R7" t="n">
-        <v>7037849</v>
+        <v>7037865</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1377,11 +1386,6 @@
           <t>2026-04-23</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>På flera granar.</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1407,14 +1411,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1435,11 +1434,11 @@
         <v>133315978</v>
       </c>
       <c r="B8" t="n">
-        <v>79358</v>
+        <v>79373</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1553,14 +1552,14 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>133315983</v>
+        <v>133315979</v>
       </c>
       <c r="B9" t="n">
-        <v>79358</v>
+        <v>79373</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1591,10 +1590,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>495380</v>
+        <v>495424</v>
       </c>
       <c r="R9" t="n">
-        <v>7037904</v>
+        <v>7037812</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1659,14 +1658,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1684,32 +1678,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>133315927</v>
+        <v>133315980</v>
       </c>
       <c r="B10" t="n">
-        <v>80478</v>
+        <v>79373</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1722,10 +1716,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>495408</v>
+        <v>495371</v>
       </c>
       <c r="R10" t="n">
-        <v>7037910</v>
+        <v>7037824</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1760,6 +1754,11 @@
           <t>2026-04-23</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>På flera granar.</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1777,22 +1776,17 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>rönn</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Sorbus aucuparia</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1810,14 +1804,14 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>133315986</v>
+        <v>133315982</v>
       </c>
       <c r="B11" t="n">
-        <v>79358</v>
+        <v>79373</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -1848,10 +1842,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>495529</v>
+        <v>495349</v>
       </c>
       <c r="R11" t="n">
-        <v>7037915</v>
+        <v>7037870</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1884,6 +1878,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1931,14 +1930,14 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>133315985</v>
+        <v>133315983</v>
       </c>
       <c r="B12" t="n">
-        <v>79358</v>
+        <v>79373</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -1969,10 +1968,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>495575</v>
+        <v>495380</v>
       </c>
       <c r="R12" t="n">
-        <v>7037913</v>
+        <v>7037904</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2007,6 +2006,11 @@
           <t>2026-04-23</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>På flera granar.</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -2032,9 +2036,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2052,14 +2061,14 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>133315979</v>
+        <v>133315984</v>
       </c>
       <c r="B13" t="n">
-        <v>79358</v>
+        <v>79373</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -2090,10 +2099,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>495424</v>
+        <v>495402</v>
       </c>
       <c r="R13" t="n">
-        <v>7037812</v>
+        <v>7037913</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2126,11 +2135,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2178,41 +2182,37 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133315937</v>
+        <v>133315985</v>
       </c>
       <c r="B14" t="n">
-        <v>80473</v>
+        <v>79373</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2220,10 +2220,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>495519</v>
+        <v>495575</v>
       </c>
       <c r="R14" t="n">
-        <v>7037889</v>
+        <v>7037913</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2275,22 +2275,17 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2308,14 +2303,14 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>133315980</v>
+        <v>133315986</v>
       </c>
       <c r="B15" t="n">
-        <v>79358</v>
+        <v>79373</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -2346,10 +2341,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>495371</v>
+        <v>495529</v>
       </c>
       <c r="R15" t="n">
-        <v>7037824</v>
+        <v>7037915</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2382,11 +2377,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2434,14 +2424,14 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>133315973</v>
+        <v>133315987</v>
       </c>
       <c r="B16" t="n">
-        <v>79358</v>
+        <v>79373</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -2472,10 +2462,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>495614</v>
+        <v>495529</v>
       </c>
       <c r="R16" t="n">
-        <v>7037811</v>
+        <v>7037845</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2555,14 +2545,14 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>133315972</v>
+        <v>133315988</v>
       </c>
       <c r="B17" t="n">
-        <v>79358</v>
+        <v>79373</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -2593,10 +2583,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>495661</v>
+        <v>495567</v>
       </c>
       <c r="R17" t="n">
-        <v>7037824</v>
+        <v>7037770</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2661,14 +2651,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2686,14 +2671,14 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>133315976</v>
+        <v>133315990</v>
       </c>
       <c r="B18" t="n">
-        <v>79358</v>
+        <v>79373</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
@@ -2724,10 +2709,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>495495</v>
+        <v>495609</v>
       </c>
       <c r="R18" t="n">
-        <v>7037847</v>
+        <v>7037717</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2779,7 +2764,7 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
@@ -2792,9 +2777,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM18" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2812,32 +2802,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>133315930</v>
+        <v>133315935</v>
       </c>
       <c r="B19" t="n">
-        <v>80478</v>
+        <v>80488</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2850,10 +2840,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>495521</v>
+        <v>495542</v>
       </c>
       <c r="R19" t="n">
-        <v>7037893</v>
+        <v>7037951</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2913,9 +2903,14 @@
           <t>Salix caprea</t>
         </is>
       </c>
+      <c r="AM19" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2933,10 +2928,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>133315987</v>
+        <v>133315937</v>
       </c>
       <c r="B20" t="n">
-        <v>79358</v>
+        <v>80488</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2944,26 +2939,30 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2971,10 +2970,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>495529</v>
+        <v>495519</v>
       </c>
       <c r="R20" t="n">
-        <v>7037845</v>
+        <v>7037889</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3021,22 +3020,27 @@
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM20" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3054,32 +3058,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>133315988</v>
+        <v>133315927</v>
       </c>
       <c r="B21" t="n">
-        <v>79358</v>
+        <v>80493</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -3092,10 +3096,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>495567</v>
+        <v>495408</v>
       </c>
       <c r="R21" t="n">
-        <v>7037770</v>
+        <v>7037910</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3130,11 +3134,6 @@
           <t>2026-04-23</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>På flera granar.</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
@@ -3147,22 +3146,27 @@
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>rönn</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AM21" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3180,10 +3184,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>133315929</v>
+        <v>133315928</v>
       </c>
       <c r="B22" t="n">
-        <v>80478</v>
+        <v>80493</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3210,7 +3214,11 @@
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -3218,10 +3226,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>495557</v>
+        <v>495542</v>
       </c>
       <c r="R22" t="n">
-        <v>7037955</v>
+        <v>7037951</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3281,9 +3289,14 @@
           <t>Salix caprea</t>
         </is>
       </c>
+      <c r="AM22" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3301,32 +3314,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>133315935</v>
+        <v>133315929</v>
       </c>
       <c r="B23" t="n">
-        <v>80473</v>
+        <v>80493</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3339,10 +3352,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>495542</v>
+        <v>495557</v>
       </c>
       <c r="R23" t="n">
-        <v>7037951</v>
+        <v>7037955</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3402,14 +3415,9 @@
           <t>Salix caprea</t>
         </is>
       </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3427,10 +3435,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>133315928</v>
+        <v>133315930</v>
       </c>
       <c r="B24" t="n">
-        <v>80478</v>
+        <v>80493</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3457,11 +3465,7 @@
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3469,10 +3473,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>495542</v>
+        <v>495521</v>
       </c>
       <c r="R24" t="n">
-        <v>7037951</v>
+        <v>7037893</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3532,14 +3536,9 @@
           <t>Salix caprea</t>
         </is>
       </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3557,40 +3556,39 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>133315910</v>
+        <v>133315942</v>
       </c>
       <c r="B25" t="n">
-        <v>57975</v>
+        <v>80500</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N25" t="inlineStr"/>
@@ -3600,10 +3598,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>495562</v>
+        <v>495453</v>
       </c>
       <c r="R25" t="n">
-        <v>7037802</v>
+        <v>7037883</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3640,7 +3638,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre, längs flera meter på en gran.</t>
+          <t>På rönn.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3649,32 +3647,28 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>rönn</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
         <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
+          <t>Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3692,7 +3686,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>133315903</v>
+        <v>133315902</v>
       </c>
       <c r="B26" t="n">
         <v>57975</v>
@@ -3735,10 +3729,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>495408</v>
+        <v>495518</v>
       </c>
       <c r="R26" t="n">
-        <v>7037812</v>
+        <v>7037832</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3775,7 +3769,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, längs flera meter på en gran.</t>
+          <t>Ringhack, äldre, på en gran.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3789,7 +3783,7 @@
       </c>
       <c r="AH26" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ26" t="inlineStr">
@@ -3822,7 +3816,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>133315907</v>
+        <v>133315903</v>
       </c>
       <c r="B27" t="n">
         <v>57975</v>
@@ -3865,10 +3859,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>495346</v>
+        <v>495408</v>
       </c>
       <c r="R27" t="n">
-        <v>7037895</v>
+        <v>7037812</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3952,7 +3946,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>133315905</v>
+        <v>133315904</v>
       </c>
       <c r="B28" t="n">
         <v>57975</v>
@@ -3985,7 +3979,7 @@
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N28" t="inlineStr"/>
@@ -3995,10 +3989,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>495346</v>
+        <v>495360</v>
       </c>
       <c r="R28" t="n">
-        <v>7037839</v>
+        <v>7037822</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4035,7 +4029,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, längs flera meter på en gran.</t>
+          <t>Ringhack, äldre, med kådaflöden på en gran.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4062,14 +4056,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4087,7 +4076,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>133315904</v>
+        <v>133315905</v>
       </c>
       <c r="B29" t="n">
         <v>57975</v>
@@ -4120,7 +4109,7 @@
       <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N29" t="inlineStr"/>
@@ -4130,10 +4119,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>495360</v>
+        <v>495346</v>
       </c>
       <c r="R29" t="n">
-        <v>7037822</v>
+        <v>7037839</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4170,7 +4159,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, med kådaflöden på en gran.</t>
+          <t>Ringhack (savhack), färska, längs flera meter på en gran.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4197,9 +4186,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM29" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4217,7 +4211,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>133315909</v>
+        <v>133315906</v>
       </c>
       <c r="B30" t="n">
         <v>57975</v>
@@ -4250,7 +4244,7 @@
       <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N30" t="inlineStr"/>
@@ -4260,10 +4254,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>495544</v>
+        <v>495344</v>
       </c>
       <c r="R30" t="n">
-        <v>7037825</v>
+        <v>7037883</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4300,7 +4294,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran.</t>
+          <t>Ringhack, färska och äldre, längs flera meter på en gran.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4314,7 +4308,7 @@
       </c>
       <c r="AH30" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ30" t="inlineStr">
@@ -4327,9 +4321,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM30" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4347,7 +4346,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>133315906</v>
+        <v>133315907</v>
       </c>
       <c r="B31" t="n">
         <v>57975</v>
@@ -4380,7 +4379,7 @@
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N31" t="inlineStr"/>
@@ -4390,10 +4389,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>495344</v>
+        <v>495346</v>
       </c>
       <c r="R31" t="n">
-        <v>7037883</v>
+        <v>7037895</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4430,7 +4429,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre, längs flera meter på en gran.</t>
+          <t>Ringhack, äldre, längs flera meter på en gran.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4457,14 +4456,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4479,6 +4473,751 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>133315908</v>
+      </c>
+      <c r="B32" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Erik-Nilsabodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>495346</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7037922</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en gran.</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH32" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>133315909</v>
+      </c>
+      <c r="B33" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Erik-Nilsabodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>495544</v>
+      </c>
+      <c r="R33" t="n">
+        <v>7037825</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en gran.</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH33" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>133315910</v>
+      </c>
+      <c r="B34" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Erik-Nilsabodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>495562</v>
+      </c>
+      <c r="R34" t="n">
+        <v>7037802</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Ringhack, färska och äldre, längs flera meter på en gran.</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH34" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM34" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>133315943</v>
+      </c>
+      <c r="B35" t="n">
+        <v>111153</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>220240</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Linnea</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Linnaea borealis</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Erik-Nilsabodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>495656</v>
+      </c>
+      <c r="R35" t="n">
+        <v>7037779</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF35" t="inlineStr"/>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH35" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>133315944</v>
+      </c>
+      <c r="B36" t="n">
+        <v>111153</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>220240</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Linnea</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Linnaea borealis</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Erik-Nilsabodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>495528</v>
+      </c>
+      <c r="R36" t="n">
+        <v>7037854</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF36" t="inlineStr"/>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH36" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>133315960</v>
+      </c>
+      <c r="B37" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr"/>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Erik-Nilsabodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>495588</v>
+      </c>
+      <c r="R37" t="n">
+        <v>7037838</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Minst 36 plantor inom ca 1 m2 yta intill en stående död gran och en tall.</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF37" t="inlineStr"/>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH37" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 17248-2026 artfynd.xlsx
+++ b/artfynd/A 17248-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY37"/>
+  <dimension ref="A1:AZ37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -798,6 +803,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133315970</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -929,6 +939,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133315972</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1050,6 +1065,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133315973</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1181,6 +1201,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133315974</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1307,6 +1332,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133315976</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1428,6 +1458,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133315977</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1549,6 +1584,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133315978</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1675,6 +1715,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133315979</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1801,6 +1846,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133315980</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1927,6 +1977,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133315982</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -2058,6 +2113,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133315983</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2179,6 +2239,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133315984</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2300,6 +2365,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133315985</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2421,6 +2491,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133315986</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2542,6 +2617,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133315987</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2668,6 +2748,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133315988</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2799,6 +2884,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133315990</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2925,6 +3015,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133315935</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -3055,6 +3150,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133315937</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3181,6 +3281,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133315927</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3311,6 +3416,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133315928</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3432,6 +3542,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133315929</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3553,6 +3668,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133315930</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3683,6 +3803,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133315942</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3813,6 +3938,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133315902</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3943,6 +4073,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133315903</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -4073,6 +4208,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133315904</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -4208,6 +4348,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133315905</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -4343,6 +4488,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133315906</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4473,6 +4623,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133315907</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4603,6 +4758,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133315908</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4733,6 +4893,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133315909</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4868,6 +5033,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133315910</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4979,6 +5149,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133315943</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -5090,6 +5265,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133315944</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -5218,8 +5398,51 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133315960</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>